--- a/etf_holdings/2026-10-16_00982A_full_holdings.xlsx
+++ b/etf_holdings/2026-10-16_00982A_full_holdings.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M16"/>
+  <dimension ref="A1:M57"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -491,7 +491,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-10-16 21:31:22</t>
+          <t>2026-10-16 21:58:06</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -509,18 +509,16 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>——</t>
+          <t>-0.82%2420</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+          <t>-0.82%</t>
+        </is>
+      </c>
+      <c r="H2" t="n">
+        <v>2420</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
@@ -537,7 +535,7 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-0.07%</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
@@ -554,7 +552,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-10-16 21:31:22</t>
+          <t>2026-10-16 21:58:06</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -572,18 +570,16 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>——</t>
+          <t>+2.04%4250</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+          <t>+2.04%</t>
+        </is>
+      </c>
+      <c r="H3" t="n">
+        <v>4250</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
@@ -600,7 +596,7 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>+0.13%</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
@@ -617,7 +613,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-10-16 21:31:22</t>
+          <t>2026-10-16 21:58:06</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -635,18 +631,16 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>——</t>
+          <t>-0.2%501</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+          <t>-0.2%</t>
+        </is>
+      </c>
+      <c r="H4" t="n">
+        <v>501</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
@@ -663,7 +657,7 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-0.01%</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
@@ -680,7 +674,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-10-16 21:31:22</t>
+          <t>2026-10-16 21:58:06</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -698,18 +692,16 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>——</t>
+          <t>-1.88%677</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+          <t>-1.88%</t>
+        </is>
+      </c>
+      <c r="H5" t="n">
+        <v>677</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
@@ -726,7 +718,7 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-0.11%</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
@@ -743,7 +735,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-10-16 21:31:22</t>
+          <t>2026-10-16 21:58:06</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -761,18 +753,16 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>——</t>
+          <t>-3.15%1845</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+          <t>-3.15%</t>
+        </is>
+      </c>
+      <c r="H6" t="n">
+        <v>1845</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
@@ -789,7 +779,7 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-0.13%</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
@@ -806,7 +796,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-10-16 21:31:22</t>
+          <t>2026-10-16 21:58:06</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -824,18 +814,16 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>——</t>
+          <t>+6.14%882</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+          <t>+6.14%</t>
+        </is>
+      </c>
+      <c r="H7" t="n">
+        <v>882</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
@@ -852,7 +840,7 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>+0.22%</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
@@ -869,7 +857,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-10-16 21:31:22</t>
+          <t>2026-10-16 21:58:06</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -887,18 +875,16 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>——</t>
+          <t>-1.23%2000</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+          <t>-1.23%</t>
+        </is>
+      </c>
+      <c r="H8" t="n">
+        <v>2000</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
@@ -915,7 +901,7 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-0.05%</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
@@ -932,7 +918,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-10-16 21:31:22</t>
+          <t>2026-10-16 21:58:06</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -950,18 +936,16 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>——</t>
+          <t>-3.1%6400</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+          <t>-3.1%</t>
+        </is>
+      </c>
+      <c r="H9" t="n">
+        <v>6400</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
@@ -978,7 +962,7 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-0.11%</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
@@ -995,7 +979,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-10-16 21:31:22</t>
+          <t>2026-10-16 21:58:06</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1013,18 +997,16 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>——</t>
+          <t>+7.32%557</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+          <t>+7.32%</t>
+        </is>
+      </c>
+      <c r="H10" t="n">
+        <v>557</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
@@ -1041,7 +1023,7 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>+0.24%</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
@@ -1058,7 +1040,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-10-16 21:31:22</t>
+          <t>2026-10-16 21:58:06</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1076,18 +1058,16 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>——</t>
+          <t>-1.79%5205</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+          <t>-1.79%</t>
+        </is>
+      </c>
+      <c r="H11" t="n">
+        <v>5205</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
@@ -1104,7 +1084,7 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-0.06%</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
@@ -1121,7 +1101,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-10-16 21:31:22</t>
+          <t>2026-10-16 21:58:06</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1139,18 +1119,16 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>——</t>
+          <t>+0.88%5165</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+          <t>+0.88%</t>
+        </is>
+      </c>
+      <c r="H12" t="n">
+        <v>5165</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
@@ -1167,7 +1145,7 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>+0.03%</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
@@ -1184,7 +1162,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-10-16 21:31:22</t>
+          <t>2026-10-16 21:58:06</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1202,18 +1180,16 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>——</t>
+          <t>+9.81%1455</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H13" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+          <t>+9.81%</t>
+        </is>
+      </c>
+      <c r="H13" t="n">
+        <v>1455</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
@@ -1230,7 +1206,7 @@
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>+0.30%</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
@@ -1247,7 +1223,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-10-16 21:31:22</t>
+          <t>2026-10-16 21:58:06</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1265,18 +1241,16 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>——</t>
+          <t>+2.42%9955</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H14" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+          <t>+2.42%</t>
+        </is>
+      </c>
+      <c r="H14" t="n">
+        <v>9955</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
@@ -1293,7 +1267,7 @@
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>+0.06%</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
@@ -1310,7 +1284,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-10-16 21:31:22</t>
+          <t>2026-10-16 21:58:06</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1328,18 +1302,16 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>——</t>
+          <t>+7.46%3315</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H15" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+          <t>+7.46%</t>
+        </is>
+      </c>
+      <c r="H15" t="n">
+        <v>3315</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
@@ -1356,7 +1328,7 @@
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>+0.17%</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
@@ -1373,7 +1345,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-10-16 21:31:22</t>
+          <t>2026-10-16 21:58:06</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1391,18 +1363,16 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>——</t>
+          <t>-2.28%902</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H16" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+          <t>-2.28%</t>
+        </is>
+      </c>
+      <c r="H16" t="n">
+        <v>902</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
@@ -1419,10 +1389,2511 @@
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-0.05%</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
+        <is>
+          <t>登入查看</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>00982A</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>2026-10-16 21:58:08</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>https://www.etfinfo.tw/etf/00982A/holdings</t>
+        </is>
+      </c>
+      <c r="D17" t="n">
+        <v>2</v>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>3265台星科</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>-3.24%269</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>-3.24%</t>
+        </is>
+      </c>
+      <c r="H17" t="n">
+        <v>269</v>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>1.98%3,345,000</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>1.98%</t>
+        </is>
+      </c>
+      <c r="K17" t="n">
+        <v>3345000</v>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>-0.07%</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>登入查看</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>00982A</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>2026-10-16 21:58:08</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>https://www.etfinfo.tw/etf/00982A/holdings</t>
+        </is>
+      </c>
+      <c r="D18" t="n">
+        <v>2</v>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>2301光寶科</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>-1.31%264.5</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>-1.31%</t>
+        </is>
+      </c>
+      <c r="H18" t="n">
+        <v>264.5</v>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>1.84%3,216,000</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>1.84%</t>
+        </is>
+      </c>
+      <c r="K18" t="n">
+        <v>3216000</v>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>-0.02%</t>
+        </is>
+      </c>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>登入查看</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>00982A</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>2026-10-16 21:58:08</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>https://www.etfinfo.tw/etf/00982A/holdings</t>
+        </is>
+      </c>
+      <c r="D19" t="n">
+        <v>2</v>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>6213聯茂</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>-3.13%774</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>-3.13%</t>
+        </is>
+      </c>
+      <c r="H19" t="n">
+        <v>774</v>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>1.60%940,000</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>1.60%</t>
+        </is>
+      </c>
+      <c r="K19" t="n">
+        <v>940000</v>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>-0.05%</t>
+        </is>
+      </c>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>登入查看</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>00982A</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>2026-10-16 21:58:08</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>https://www.etfinfo.tw/etf/00982A/holdings</t>
+        </is>
+      </c>
+      <c r="D20" t="n">
+        <v>2</v>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>2455全新</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>+1.96%493</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>+1.96%</t>
+        </is>
+      </c>
+      <c r="H20" t="n">
+        <v>493</v>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>1.58%1,529,000</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>1.58%</t>
+        </is>
+      </c>
+      <c r="K20" t="n">
+        <v>1529000</v>
+      </c>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>+0.03%</t>
+        </is>
+      </c>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>登入查看</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>00982A</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>2026-10-16 21:58:08</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>https://www.etfinfo.tw/etf/00982A/holdings</t>
+        </is>
+      </c>
+      <c r="D21" t="n">
+        <v>2</v>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>2303聯電</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>-0.37%133</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>-0.37%</t>
+        </is>
+      </c>
+      <c r="H21" t="n">
+        <v>133</v>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>1.46%5,116,000</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>1.46%</t>
+        </is>
+      </c>
+      <c r="K21" t="n">
+        <v>5116000</v>
+      </c>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>-0.01%</t>
+        </is>
+      </c>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>登入查看</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>00982A</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>2026-10-16 21:58:08</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>https://www.etfinfo.tw/etf/00982A/holdings</t>
+        </is>
+      </c>
+      <c r="D22" t="n">
+        <v>2</v>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>6274台燿</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>-0.62%1615</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>-0.62%</t>
+        </is>
+      </c>
+      <c r="H22" t="n">
+        <v>1615</v>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>1.45%418,000</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>1.45%</t>
+        </is>
+      </c>
+      <c r="K22" t="n">
+        <v>418000</v>
+      </c>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>-0.01%</t>
+        </is>
+      </c>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>登入查看</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>00982A</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>2026-10-16 21:58:08</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>https://www.etfinfo.tw/etf/00982A/holdings</t>
+        </is>
+      </c>
+      <c r="D23" t="n">
+        <v>2</v>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>6214精誠</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>+0.25%197.5</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>+0.25%</t>
+        </is>
+      </c>
+      <c r="H23" t="n">
+        <v>197.5</v>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>1.44%3,438,000</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>1.44%</t>
+        </is>
+      </c>
+      <c r="K23" t="n">
+        <v>3438000</v>
+      </c>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>+0.00%</t>
+        </is>
+      </c>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>登入查看</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>00982A</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>2026-10-16 21:58:08</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>https://www.etfinfo.tw/etf/00982A/holdings</t>
+        </is>
+      </c>
+      <c r="D24" t="n">
+        <v>2</v>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>2395研華</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>-1.86%685</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>-1.86%</t>
+        </is>
+      </c>
+      <c r="H24" t="n">
+        <v>685</v>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>1.43%964,000</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>1.43%</t>
+        </is>
+      </c>
+      <c r="K24" t="n">
+        <v>964000</v>
+      </c>
+      <c r="L24" t="inlineStr">
+        <is>
+          <t>-0.03%</t>
+        </is>
+      </c>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>登入查看</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>00982A</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>2026-10-16 21:58:08</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>https://www.etfinfo.tw/etf/00982A/holdings</t>
+        </is>
+      </c>
+      <c r="D25" t="n">
+        <v>2</v>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>5483中美晶</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>+2.3%200</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>+2.3%</t>
+        </is>
+      </c>
+      <c r="H25" t="n">
+        <v>200</v>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>1.42%3,415,000</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>1.42%</t>
+        </is>
+      </c>
+      <c r="K25" t="n">
+        <v>3415000</v>
+      </c>
+      <c r="L25" t="inlineStr">
+        <is>
+          <t>+0.03%</t>
+        </is>
+      </c>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>登入查看</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>00982A</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>2026-10-16 21:58:08</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>https://www.etfinfo.tw/etf/00982A/holdings</t>
+        </is>
+      </c>
+      <c r="D26" t="n">
+        <v>2</v>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>3231緯創</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>+3.69%182.5</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>+3.69%</t>
+        </is>
+      </c>
+      <c r="H26" t="n">
+        <v>182.5</v>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>1.36%3,638,000</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>1.36%</t>
+        </is>
+      </c>
+      <c r="K26" t="n">
+        <v>3638000</v>
+      </c>
+      <c r="L26" t="inlineStr">
+        <is>
+          <t>+0.05%</t>
+        </is>
+      </c>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>登入查看</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>00982A</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>2026-10-16 21:58:08</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>https://www.etfinfo.tw/etf/00982A/holdings</t>
+        </is>
+      </c>
+      <c r="D27" t="n">
+        <v>2</v>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>2478大毅</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>-6.34%133</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>-6.34%</t>
+        </is>
+      </c>
+      <c r="H27" t="n">
+        <v>133</v>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>1.31%4,331,000</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>1.31%</t>
+        </is>
+      </c>
+      <c r="K27" t="n">
+        <v>4331000</v>
+      </c>
+      <c r="L27" t="inlineStr">
+        <is>
+          <t>-0.09%</t>
+        </is>
+      </c>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>登入查看</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>00982A</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>2026-10-16 21:58:08</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>https://www.etfinfo.tw/etf/00982A/holdings</t>
+        </is>
+      </c>
+      <c r="D28" t="n">
+        <v>2</v>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>2428興勤</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>-1.69%261.5</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>-1.69%</t>
+        </is>
+      </c>
+      <c r="H28" t="n">
+        <v>261.5</v>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>1.29%2,268,000</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>1.29%</t>
+        </is>
+      </c>
+      <c r="K28" t="n">
+        <v>2268000</v>
+      </c>
+      <c r="L28" t="inlineStr">
+        <is>
+          <t>-0.02%</t>
+        </is>
+      </c>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>登入查看</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>00982A</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>2026-10-16 21:58:08</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>https://www.etfinfo.tw/etf/00982A/holdings</t>
+        </is>
+      </c>
+      <c r="D29" t="n">
+        <v>2</v>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>2376技嘉</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>+3.03%357.5</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>+3.03%</t>
+        </is>
+      </c>
+      <c r="H29" t="n">
+        <v>357.5</v>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>1.28%1,737,000</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>1.28%</t>
+        </is>
+      </c>
+      <c r="K29" t="n">
+        <v>1737000</v>
+      </c>
+      <c r="L29" t="inlineStr">
+        <is>
+          <t>+0.04%</t>
+        </is>
+      </c>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>登入查看</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>00982A</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>2026-10-16 21:58:08</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>https://www.etfinfo.tw/etf/00982A/holdings</t>
+        </is>
+      </c>
+      <c r="D30" t="n">
+        <v>2</v>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>5425台半</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>+0.11%92.6</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>+0.11%</t>
+        </is>
+      </c>
+      <c r="H30" t="n">
+        <v>92.59999999999999</v>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>1.26%6,382,000</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>1.26%</t>
+        </is>
+      </c>
+      <c r="K30" t="n">
+        <v>6382000</v>
+      </c>
+      <c r="L30" t="inlineStr">
+        <is>
+          <t>+0.00%</t>
+        </is>
+      </c>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>登入查看</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>00982A</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>2026-10-16 21:58:08</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>https://www.etfinfo.tw/etf/00982A/holdings</t>
+        </is>
+      </c>
+      <c r="D31" t="n">
+        <v>2</v>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>3711日月光投控</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>-0.3%671</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>-0.3%</t>
+        </is>
+      </c>
+      <c r="H31" t="n">
+        <v>671</v>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>1.26%876,000</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>1.26%</t>
+        </is>
+      </c>
+      <c r="K31" t="n">
+        <v>876000</v>
+      </c>
+      <c r="L31" t="inlineStr">
+        <is>
+          <t>-0.00%</t>
+        </is>
+      </c>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>登入查看</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>00982A</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>2026-10-16 21:58:09</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>https://www.etfinfo.tw/etf/00982A/holdings</t>
+        </is>
+      </c>
+      <c r="D32" t="n">
+        <v>3</v>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>8996高力</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>+3.29%1570</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>+3.29%</t>
+        </is>
+      </c>
+      <c r="H32" t="n">
+        <v>1570</v>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>1.24%382,000</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>1.24%</t>
+        </is>
+      </c>
+      <c r="K32" t="n">
+        <v>382000</v>
+      </c>
+      <c r="L32" t="inlineStr">
+        <is>
+          <t>+0.04%</t>
+        </is>
+      </c>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>登入查看</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>00982A</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>2026-10-16 21:58:09</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>https://www.etfinfo.tw/etf/00982A/holdings</t>
+        </is>
+      </c>
+      <c r="D33" t="n">
+        <v>3</v>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>5274信驊</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>+3.36%16480</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>+3.36%</t>
+        </is>
+      </c>
+      <c r="H33" t="n">
+        <v>16480</v>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>1.22%35,900</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>1.22%</t>
+        </is>
+      </c>
+      <c r="K33" t="n">
+        <v>35900</v>
+      </c>
+      <c r="L33" t="inlineStr">
+        <is>
+          <t>+0.04%</t>
+        </is>
+      </c>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>登入查看</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>00982A</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>2026-10-16 21:58:09</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>https://www.etfinfo.tw/etf/00982A/holdings</t>
+        </is>
+      </c>
+      <c r="D34" t="n">
+        <v>3</v>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>6672騰輝電子-KY</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>+3.68%591</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>+3.68%</t>
+        </is>
+      </c>
+      <c r="H34" t="n">
+        <v>591</v>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>1.21%994,000</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>1.21%</t>
+        </is>
+      </c>
+      <c r="K34" t="n">
+        <v>994000</v>
+      </c>
+      <c r="L34" t="inlineStr">
+        <is>
+          <t>+0.04%</t>
+        </is>
+      </c>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>登入查看</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>00982A</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>2026-10-16 21:58:09</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>https://www.etfinfo.tw/etf/00982A/holdings</t>
+        </is>
+      </c>
+      <c r="D35" t="n">
+        <v>3</v>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>3090日電貿</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>-0.58%170.5</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>-0.58%</t>
+        </is>
+      </c>
+      <c r="H35" t="n">
+        <v>170.5</v>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>1.20%3,280,000</t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>1.20%</t>
+        </is>
+      </c>
+      <c r="K35" t="n">
+        <v>3280000</v>
+      </c>
+      <c r="L35" t="inlineStr">
+        <is>
+          <t>-0.01%</t>
+        </is>
+      </c>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>登入查看</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>00982A</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>2026-10-16 21:58:09</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>https://www.etfinfo.tw/etf/00982A/holdings</t>
+        </is>
+      </c>
+      <c r="D36" t="n">
+        <v>3</v>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>6239力成</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>+1.29%274</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>+1.29%</t>
+        </is>
+      </c>
+      <c r="H36" t="n">
+        <v>274</v>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>1.10%1,910,000</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>1.10%</t>
+        </is>
+      </c>
+      <c r="K36" t="n">
+        <v>1910000</v>
+      </c>
+      <c r="L36" t="inlineStr">
+        <is>
+          <t>+0.01%</t>
+        </is>
+      </c>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>登入查看</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>00982A</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>2026-10-16 21:58:09</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>https://www.etfinfo.tw/etf/00982A/holdings</t>
+        </is>
+      </c>
+      <c r="D37" t="n">
+        <v>3</v>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>3583辛耘</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>-0.31%651</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>-0.31%</t>
+        </is>
+      </c>
+      <c r="H37" t="n">
+        <v>651</v>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>1.10%790,000</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>1.10%</t>
+        </is>
+      </c>
+      <c r="K37" t="n">
+        <v>790000</v>
+      </c>
+      <c r="L37" t="inlineStr">
+        <is>
+          <t>-0.00%</t>
+        </is>
+      </c>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>登入查看</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>00982A</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>2026-10-16 21:58:09</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>https://www.etfinfo.tw/etf/00982A/holdings</t>
+        </is>
+      </c>
+      <c r="D38" t="n">
+        <v>3</v>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>2467志聖</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>+0.4%508</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>+0.4%</t>
+        </is>
+      </c>
+      <c r="H38" t="n">
+        <v>508</v>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>1.08%1,000,000</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>1.08%</t>
+        </is>
+      </c>
+      <c r="K38" t="n">
+        <v>1000000</v>
+      </c>
+      <c r="L38" t="inlineStr">
+        <is>
+          <t>+0.00%</t>
+        </is>
+      </c>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>登入查看</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>00982A</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>2026-10-16 21:58:09</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>https://www.etfinfo.tw/etf/00982A/holdings</t>
+        </is>
+      </c>
+      <c r="D39" t="n">
+        <v>3</v>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>6472保瑞</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>+0.35%425.5</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>+0.35%</t>
+        </is>
+      </c>
+      <c r="H39" t="n">
+        <v>425.5</v>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>0.93%1,032,000</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>0.93%</t>
+        </is>
+      </c>
+      <c r="K39" t="n">
+        <v>1032000</v>
+      </c>
+      <c r="L39" t="inlineStr">
+        <is>
+          <t>+0.00%</t>
+        </is>
+      </c>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>登入查看</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>00982A</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>2026-10-16 21:58:09</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>https://www.etfinfo.tw/etf/00982A/holdings</t>
+        </is>
+      </c>
+      <c r="D40" t="n">
+        <v>3</v>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>5536聖暉*</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>-1.49%857</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>-1.49%</t>
+        </is>
+      </c>
+      <c r="H40" t="n">
+        <v>857</v>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>0.84%455,000</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>0.84%</t>
+        </is>
+      </c>
+      <c r="K40" t="n">
+        <v>455000</v>
+      </c>
+      <c r="L40" t="inlineStr">
+        <is>
+          <t>-0.01%</t>
+        </is>
+      </c>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>登入查看</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>00982A</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>2026-10-16 21:58:09</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>https://www.etfinfo.tw/etf/00982A/holdings</t>
+        </is>
+      </c>
+      <c r="D41" t="n">
+        <v>3</v>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>2486一詮</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>+1.89%216</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>+1.89%</t>
+        </is>
+      </c>
+      <c r="H41" t="n">
+        <v>216</v>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>0.73%1,607,000</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>0.73%</t>
+        </is>
+      </c>
+      <c r="K41" t="n">
+        <v>1607000</v>
+      </c>
+      <c r="L41" t="inlineStr">
+        <is>
+          <t>+0.01%</t>
+        </is>
+      </c>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>登入查看</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>00982A</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>2026-10-16 21:58:09</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>https://www.etfinfo.tw/etf/00982A/holdings</t>
+        </is>
+      </c>
+      <c r="D42" t="n">
+        <v>3</v>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>8070長華*</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>+1.36%52.2</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>+1.36%</t>
+        </is>
+      </c>
+      <c r="H42" t="n">
+        <v>52.2</v>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>0.47%4,312,000</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>0.47%</t>
+        </is>
+      </c>
+      <c r="K42" t="n">
+        <v>4312000</v>
+      </c>
+      <c r="L42" t="inlineStr">
+        <is>
+          <t>+0.01%</t>
+        </is>
+      </c>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>登入查看</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>00982A</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>2026-10-16 21:58:09</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>https://www.etfinfo.tw/etf/00982A/holdings</t>
+        </is>
+      </c>
+      <c r="D43" t="n">
+        <v>3</v>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>6196帆宣</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>-0.65%609</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>-0.65%</t>
+        </is>
+      </c>
+      <c r="H43" t="n">
+        <v>609</v>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>0.40%304,000</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>0.40%</t>
+        </is>
+      </c>
+      <c r="K43" t="n">
+        <v>304000</v>
+      </c>
+      <c r="L43" t="inlineStr">
+        <is>
+          <t>-0.00%</t>
+        </is>
+      </c>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>登入查看</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>00982A</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>2026-10-16 21:58:09</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>https://www.etfinfo.tw/etf/00982A/holdings</t>
+        </is>
+      </c>
+      <c r="D44" t="n">
+        <v>3</v>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>3617碩天</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>+1.34%264.5</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>+1.34%</t>
+        </is>
+      </c>
+      <c r="H44" t="n">
+        <v>264.5</v>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>0.35%627,000</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>0.35%</t>
+        </is>
+      </c>
+      <c r="K44" t="n">
+        <v>627000</v>
+      </c>
+      <c r="L44" t="inlineStr">
+        <is>
+          <t>+0.00%</t>
+        </is>
+      </c>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>登入查看</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>00982A</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>2026-10-16 21:58:09</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>https://www.etfinfo.tw/etf/00982A/holdings</t>
+        </is>
+      </c>
+      <c r="D45" t="n">
+        <v>3</v>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>2377微星</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>+2.22%161.5</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>+2.22%</t>
+        </is>
+      </c>
+      <c r="H45" t="n">
+        <v>161.5</v>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>0.34%1,022,000</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>0.34%</t>
+        </is>
+      </c>
+      <c r="K45" t="n">
+        <v>1022000</v>
+      </c>
+      <c r="L45" t="inlineStr">
+        <is>
+          <t>+0.01%</t>
+        </is>
+      </c>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>登入查看</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>00982A</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>2026-10-16 21:58:09</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>https://www.etfinfo.tw/etf/00982A/holdings</t>
+        </is>
+      </c>
+      <c r="D46" t="n">
+        <v>3</v>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>2885元大金</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>+0.28%72.9</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>+0.28%</t>
+        </is>
+      </c>
+      <c r="H46" t="n">
+        <v>72.90000000000001</v>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>0.34%2,213,556</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>0.34%</t>
+        </is>
+      </c>
+      <c r="K46" t="n">
+        <v>2213556</v>
+      </c>
+      <c r="L46" t="inlineStr">
+        <is>
+          <t>+0.00%</t>
+        </is>
+      </c>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>登入查看</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>00982A</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>2026-10-16 21:58:11</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>https://www.etfinfo.tw/etf/00982A/holdings</t>
+        </is>
+      </c>
+      <c r="D47" t="n">
+        <v>4</v>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>2476鉅祥</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>+1.23%123.5</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>+1.23%</t>
+        </is>
+      </c>
+      <c r="H47" t="n">
+        <v>123.5</v>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>0.33%1,281,000</t>
+        </is>
+      </c>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>0.33%</t>
+        </is>
+      </c>
+      <c r="K47" t="n">
+        <v>1281000</v>
+      </c>
+      <c r="L47" t="inlineStr">
+        <is>
+          <t>+0.00%</t>
+        </is>
+      </c>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>登入查看</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>00982A</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>2026-10-16 21:58:11</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>https://www.etfinfo.tw/etf/00982A/holdings</t>
+        </is>
+      </c>
+      <c r="D48" t="n">
+        <v>4</v>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>6640均華</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>0%1015</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="H48" t="n">
+        <v>1015</v>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>0.31%143,000</t>
+        </is>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>0.31%</t>
+        </is>
+      </c>
+      <c r="K48" t="n">
+        <v>143000</v>
+      </c>
+      <c r="L48" t="inlineStr">
+        <is>
+          <t>+0.00%</t>
+        </is>
+      </c>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>登入查看</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>00982A</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>2026-10-16 21:58:11</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>https://www.etfinfo.tw/etf/00982A/holdings</t>
+        </is>
+      </c>
+      <c r="D49" t="n">
+        <v>4</v>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>6446藥華藥</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>+3.32%1245</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>+3.32%</t>
+        </is>
+      </c>
+      <c r="H49" t="n">
+        <v>1245</v>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>0.11%42,000</t>
+        </is>
+      </c>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>0.11%</t>
+        </is>
+      </c>
+      <c r="K49" t="n">
+        <v>42000</v>
+      </c>
+      <c r="L49" t="inlineStr">
+        <is>
+          <t>+0.00%</t>
+        </is>
+      </c>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>登入查看</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>00982A</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>2026-10-16 21:58:11</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>https://www.etfinfo.tw/etf/00982A/holdings</t>
+        </is>
+      </c>
+      <c r="D50" t="n">
+        <v>4</v>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>6177達麗</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>+0.66%45.95</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>+0.66%</t>
+        </is>
+      </c>
+      <c r="H50" t="n">
+        <v>45.95</v>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>0.02%194,350</t>
+        </is>
+      </c>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>0.02%</t>
+        </is>
+      </c>
+      <c r="K50" t="n">
+        <v>194350</v>
+      </c>
+      <c r="L50" t="inlineStr">
+        <is>
+          <t>+0.00%</t>
+        </is>
+      </c>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>登入查看</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>00982A</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>2026-10-16 21:58:11</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>https://www.etfinfo.tw/etf/00982A/holdings</t>
+        </is>
+      </c>
+      <c r="D51" t="n">
+        <v>4</v>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>3443創意</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>-2.48%7480</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>-2.48%</t>
+        </is>
+      </c>
+      <c r="H51" t="n">
+        <v>7480</v>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>0.02%1,000</t>
+        </is>
+      </c>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>0.02%</t>
+        </is>
+      </c>
+      <c r="K51" t="n">
+        <v>1000</v>
+      </c>
+      <c r="L51" t="inlineStr">
+        <is>
+          <t>-0.00%</t>
+        </is>
+      </c>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>登入查看</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>00982A</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>2026-10-16 21:58:11</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>https://www.etfinfo.tw/etf/00982A/holdings</t>
+        </is>
+      </c>
+      <c r="D52" t="n">
+        <v>4</v>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>3529力旺</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>+3.58%2750</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>+3.58%</t>
+        </is>
+      </c>
+      <c r="H52" t="n">
+        <v>2750</v>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>&lt;0.01%1,000</t>
+        </is>
+      </c>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>&lt;0.01%</t>
+        </is>
+      </c>
+      <c r="K52" t="n">
+        <v>1000</v>
+      </c>
+      <c r="L52" t="inlineStr">
+        <is>
+          <t>+0.00%</t>
+        </is>
+      </c>
+      <c r="M52" t="inlineStr">
+        <is>
+          <t>登入查看</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>00982A</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>2026-10-16 21:58:11</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>https://www.etfinfo.tw/etf/00982A/holdings</t>
+        </is>
+      </c>
+      <c r="D53" t="n">
+        <v>4</v>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>4441振大環球</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>-0.3%167.5</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>-0.3%</t>
+        </is>
+      </c>
+      <c r="H53" t="n">
+        <v>167.5</v>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>&lt;0.01%4,000</t>
+        </is>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>&lt;0.01%</t>
+        </is>
+      </c>
+      <c r="K53" t="n">
+        <v>4000</v>
+      </c>
+      <c r="L53" t="inlineStr">
+        <is>
+          <t>-0.00%</t>
+        </is>
+      </c>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>登入查看</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>00982A</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>2026-10-16 21:58:11</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>https://www.etfinfo.tw/etf/00982A/holdings</t>
+        </is>
+      </c>
+      <c r="D54" t="n">
+        <v>4</v>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>1519華城</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>+1.08%656</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>+1.08%</t>
+        </is>
+      </c>
+      <c r="H54" t="n">
+        <v>656</v>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>&lt;0.01%660</t>
+        </is>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>&lt;0.01%</t>
+        </is>
+      </c>
+      <c r="K54" t="n">
+        <v>660</v>
+      </c>
+      <c r="L54" t="inlineStr">
+        <is>
+          <t>+0.00%</t>
+        </is>
+      </c>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>登入查看</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>00982A</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>2026-10-16 21:58:11</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>https://www.etfinfo.tw/etf/00982A/holdings</t>
+        </is>
+      </c>
+      <c r="D55" t="n">
+        <v>4</v>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>8358金居</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>+2.28%472</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>+2.28%</t>
+        </is>
+      </c>
+      <c r="H55" t="n">
+        <v>472</v>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>&lt;0.01%1,000</t>
+        </is>
+      </c>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>&lt;0.01%</t>
+        </is>
+      </c>
+      <c r="K55" t="n">
+        <v>1000</v>
+      </c>
+      <c r="L55" t="inlineStr">
+        <is>
+          <t>+0.00%</t>
+        </is>
+      </c>
+      <c r="M55" t="inlineStr">
+        <is>
+          <t>登入查看</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>00982A</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>2026-10-16 21:58:11</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>https://www.etfinfo.tw/etf/00982A/holdings</t>
+        </is>
+      </c>
+      <c r="D56" t="n">
+        <v>4</v>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>2886兆豐金</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>+2.29%53.7</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>+2.29%</t>
+        </is>
+      </c>
+      <c r="H56" t="n">
+        <v>53.7</v>
+      </c>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>&lt;0.01%1,000</t>
+        </is>
+      </c>
+      <c r="J56" t="inlineStr">
+        <is>
+          <t>&lt;0.01%</t>
+        </is>
+      </c>
+      <c r="K56" t="n">
+        <v>1000</v>
+      </c>
+      <c r="L56" t="inlineStr">
+        <is>
+          <t>+0.00%</t>
+        </is>
+      </c>
+      <c r="M56" t="inlineStr">
+        <is>
+          <t>登入查看</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>00982A</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>2026-10-16 21:58:11</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>https://www.etfinfo.tw/etf/00982A/holdings</t>
+        </is>
+      </c>
+      <c r="D57" t="n">
+        <v>4</v>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>2881富邦金</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>+1.25%161.5</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>+1.25%</t>
+        </is>
+      </c>
+      <c r="H57" t="n">
+        <v>161.5</v>
+      </c>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>0%250</t>
+        </is>
+      </c>
+      <c r="J57" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="K57" t="n">
+        <v>250</v>
+      </c>
+      <c r="L57" t="inlineStr">
+        <is>
+          <t>+0.00%</t>
+        </is>
+      </c>
+      <c r="M57" t="inlineStr">
         <is>
           <t>登入查看</t>
         </is>
